--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 102 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 99 clubs short</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,8 +1779,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -16794,7 +16794,7 @@
         <v>0</v>
       </c>
       <c r="S166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166" s="9" t="n">
         <v>0</v>
@@ -17667,7 +17667,7 @@
         <v>0</v>
       </c>
       <c r="S175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T175" s="9" t="n">
         <v>0</v>
@@ -23183,7 +23183,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 99 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 93 clubs short</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5465,8 +5465,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5736,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="10" t="n">
         <v>1</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12049,11 +12049,11 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>6</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12352,8 +12352,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -21179,8 +21179,8 @@
       <c r="Y211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z211" s="9" t="n">
-        <v>0</v>
+      <c r="Z211" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA211" s="10" t="n">
         <v>1</v>
@@ -22855,7 +22855,7 @@
         </is>
       </c>
       <c r="E229" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F229" s="6" t="n">
         <v>10</v>
@@ -22925,8 +22925,8 @@
       <c r="Y229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z229" s="9" t="n">
-        <v>0</v>
+      <c r="Z229" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA229" s="10" t="n">
         <v>1</v>
@@ -23183,7 +23183,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -24536,7 +24536,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -24668,7 +24668,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 93 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3816,8 +3816,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7502,8 +7502,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7599,8 +7599,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8375,8 +8375,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8763,8 +8763,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9539,8 +9539,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11964,8 +11964,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="9" t="n">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13419,8 +13419,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -14998,7 +14998,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15068,8 +15068,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16232,8 +16232,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -16620,8 +16620,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -16911,8 +16911,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="10" t="n">
         <v>1</v>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17105,8 +17105,8 @@
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="9" t="n">
-        <v>0</v>
+      <c r="Z169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17590,8 +17590,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17687,8 +17687,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -17861,7 +17861,7 @@
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T177" s="10" t="n">
         <v>1</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18048,8 +18048,8 @@
       <c r="P179" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q179" s="9" t="n">
-        <v>1</v>
+      <c r="Q179" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -18657,8 +18657,8 @@
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -19460,7 +19460,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -19530,8 +19530,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -20015,8 +20015,8 @@
       <c r="Y199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z199" s="9" t="n">
-        <v>0</v>
+      <c r="Z199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA199" s="10" t="n">
         <v>1</v>
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -20306,8 +20306,8 @@
       <c r="Y202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z202" s="9" t="n">
-        <v>0</v>
+      <c r="Z202" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA202" s="10" t="n">
         <v>1</v>
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -20500,8 +20500,8 @@
       <c r="Y204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z204" s="9" t="n">
-        <v>0</v>
+      <c r="Z204" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA204" s="10" t="n">
         <v>1</v>
@@ -20665,7 +20665,7 @@
         </is>
       </c>
       <c r="P206" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q206" s="9" t="n">
         <v>1</v>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>10</v>
@@ -21082,8 +21082,8 @@
       <c r="Y210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z210" s="9" t="n">
-        <v>0</v>
+      <c r="Z210" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA210" s="10" t="n">
         <v>1</v>
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" s="6" t="n">
         <v>10</v>
@@ -22246,8 +22246,8 @@
       <c r="Y222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z222" s="9" t="n">
-        <v>0</v>
+      <c r="Z222" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA222" s="10" t="n">
         <v>1</v>
@@ -22467,7 +22467,7 @@
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>10</v>
@@ -22537,8 +22537,8 @@
       <c r="Y225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z225" s="9" t="n">
-        <v>0</v>
+      <c r="Z225" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA225" s="10" t="n">
         <v>1</v>
@@ -23150,7 +23150,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -23183,7 +23183,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -23249,7 +23249,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -23315,7 +23315,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23348,7 +23348,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23480,7 +23480,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -23546,7 +23546,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -23579,7 +23579,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -23612,7 +23612,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23645,7 +23645,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -23678,7 +23678,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -23711,7 +23711,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23744,7 +23744,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -23810,7 +23810,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -23876,7 +23876,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -23942,7 +23942,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -24008,7 +24008,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -24107,7 +24107,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24206,7 +24206,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -24239,7 +24239,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -24272,7 +24272,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -24305,7 +24305,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -24338,7 +24338,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -24371,7 +24371,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -24437,7 +24437,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -24470,7 +24470,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -24503,7 +24503,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -24536,7 +24536,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -24635,7 +24635,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -947,20 +947,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1141,20 +1141,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,20 +1238,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1259,7 +1259,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1335,20 +1335,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,20 +1432,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1529,20 +1529,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1550,7 +1550,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1626,20 +1626,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1731,12 +1731,12 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1744,7 +1744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,20 +1820,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1858,8 +1858,8 @@
       <c r="S12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2014,20 +2014,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,20 +2111,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="9" t="n">
         <v>0</v>
@@ -2208,20 +2208,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2229,7 +2229,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2305,20 +2305,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2402,20 +2402,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2499,20 +2499,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2520,7 +2520,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2596,20 +2596,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2693,20 +2693,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2714,7 +2714,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2790,20 +2790,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2811,7 +2811,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2908,7 +2908,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2984,20 +2984,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3081,20 +3081,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3186,12 +3186,12 @@
       <c r="K26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3275,20 +3275,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3296,7 +3296,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3323,7 +3323,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3372,20 +3372,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3469,20 +3469,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3574,12 +3574,12 @@
       <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3587,7 +3587,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3663,20 +3663,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3684,7 +3684,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3760,20 +3760,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3857,20 +3857,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3954,20 +3954,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4051,20 +4051,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4148,20 +4148,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4169,7 +4169,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4245,20 +4245,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4342,20 +4342,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4439,20 +4439,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4460,7 +4460,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4549,7 +4549,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4633,20 +4633,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4730,20 +4730,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4827,20 +4827,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4932,12 +4932,12 @@
       <c r="K44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4945,7 +4945,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5021,20 +5021,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5042,7 +5042,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5118,20 +5118,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5215,20 +5215,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5312,20 +5312,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5333,7 +5333,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5360,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>4</v>
@@ -5409,20 +5409,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5430,7 +5430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5506,20 +5506,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5527,7 +5527,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5603,20 +5603,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5624,7 +5624,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,20 +5700,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5721,13 +5721,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
         <v>1</v>
@@ -5735,14 +5735,14 @@
       <c r="R52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S52" s="9" t="n">
-        <v>1</v>
+      <c r="S52" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U52" s="9" t="n">
-        <v>0</v>
+      <c r="U52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V52" s="9" t="n">
         <v>0</v>
@@ -5797,20 +5797,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5818,13 +5818,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="10" t="n">
         <v>2</v>
@@ -5894,20 +5894,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5991,20 +5991,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6012,7 +6012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6088,20 +6088,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6109,7 +6109,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6185,20 +6185,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6282,20 +6282,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6303,7 +6303,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6379,20 +6379,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6400,7 +6400,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6484,12 +6484,12 @@
       <c r="K60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L60" s="8" t="inlineStr">
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6497,7 +6497,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6573,20 +6573,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6611,8 +6611,8 @@
       <c r="S61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -6621,7 +6621,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -6670,20 +6670,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6691,7 +6691,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6767,20 +6767,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,20 +6864,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6899,8 +6899,8 @@
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="9" t="n">
-        <v>1</v>
+      <c r="S64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T64" s="10" t="n">
         <v>1</v>
@@ -6909,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -6961,20 +6961,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7058,20 +7058,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7079,7 +7079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7155,20 +7155,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7185,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,20 +7252,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7273,7 +7273,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7357,12 +7357,12 @@
       <c r="K69" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L69" s="8" t="inlineStr">
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7446,20 +7446,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7543,20 +7543,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7564,7 +7564,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,20 +7640,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M72" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7737,20 +7737,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -7834,20 +7834,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7931,34 +7931,34 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P75" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N75" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O75" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P75" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>
@@ -8036,12 +8036,12 @@
       <c r="K76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="8" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8125,20 +8125,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8146,7 +8146,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8222,20 +8222,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8319,20 +8319,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8340,7 +8340,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8416,20 +8416,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8437,7 +8437,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,20 +8513,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8557,11 +8557,11 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>2</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>6</v>
@@ -8610,20 +8610,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -8631,7 +8631,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8707,20 +8707,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M83" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -8728,7 +8728,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8804,20 +8804,20 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -8825,7 +8825,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8901,20 +8901,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M85" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8922,7 +8922,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8998,20 +8998,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9108,7 +9108,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9116,7 +9116,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,35 +9192,35 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K88" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P88" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N88" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O88" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P88" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" s="9" t="n">
         <v>0</v>
@@ -9236,8 +9236,8 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="9" t="n">
-        <v>2</v>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9289,20 +9289,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9394,12 +9394,12 @@
       <c r="K90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="8" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9407,7 +9407,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9483,20 +9483,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9504,7 +9504,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9593,7 +9593,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9677,20 +9677,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M93" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -9698,7 +9698,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9774,20 +9774,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9871,20 +9871,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9968,20 +9968,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10065,20 +10065,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10170,12 +10170,12 @@
       <c r="K98" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="8" t="inlineStr">
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10259,20 +10259,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10280,7 +10280,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10356,20 +10356,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10377,7 +10377,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10453,20 +10453,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -10474,7 +10474,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10489,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,20 +10550,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10594,11 +10594,11 @@
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W102" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -10647,20 +10647,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -10668,7 +10668,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10744,20 +10744,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10841,20 +10841,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -10862,7 +10862,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10938,20 +10938,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -10959,7 +10959,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11035,20 +11035,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11056,7 +11056,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11132,20 +11132,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M108" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11153,7 +11153,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11229,20 +11229,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11326,20 +11326,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11347,7 +11347,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,20 +11423,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -11444,7 +11444,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11452,8 +11452,8 @@
       <c r="P111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" s="9" t="n">
-        <v>1</v>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,20 +11520,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M112" s="7" t="n">
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -11541,7 +11541,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11617,20 +11617,20 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -11638,7 +11638,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11714,20 +11714,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11811,20 +11811,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11908,20 +11908,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -11929,7 +11929,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,20 +12005,20 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12026,7 +12026,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12110,12 +12110,12 @@
       <c r="K118" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L118" s="8" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12207,12 +12207,12 @@
       <c r="K119" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="8" t="inlineStr">
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M119" s="7" t="n">
+      <c r="M119" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12220,7 +12220,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12296,20 +12296,20 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12393,20 +12393,20 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M121" s="7" t="n">
+        <v>-23</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -12414,7 +12414,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12490,20 +12490,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -12511,7 +12511,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12587,20 +12587,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="7" t="n">
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -12608,7 +12608,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12684,20 +12684,20 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -12705,7 +12705,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12781,20 +12781,20 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M125" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M125" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -12802,7 +12802,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12829,7 +12829,7 @@
         <v>4</v>
       </c>
       <c r="W125" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>4</v>
@@ -12886,12 +12886,12 @@
       <c r="K126" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="8" t="inlineStr">
+      <c r="L126" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M126" s="7" t="n">
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -12899,7 +12899,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12975,20 +12975,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M127" s="7" t="n">
+      <c r="M127" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -12996,7 +12996,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="8" t="inlineStr">
+      <c r="O127" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13072,20 +13072,20 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M128" s="7" t="n">
+      <c r="M128" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13093,7 +13093,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,20 +13169,20 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M129" s="7" t="n">
+      <c r="M129" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13190,7 +13190,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13213,8 +13213,8 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13266,20 +13266,20 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M130" s="7" t="n">
+      <c r="M130" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -13287,7 +13287,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="8" t="inlineStr">
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13371,12 +13371,12 @@
       <c r="K131" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L131" s="8" t="inlineStr">
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M131" s="7" t="n">
+      <c r="M131" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -13384,7 +13384,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="O131" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13460,20 +13460,20 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M132" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -13481,7 +13481,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="8" t="inlineStr">
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13557,20 +13557,20 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M133" s="7" t="n">
+      <c r="M133" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -13578,7 +13578,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O133" s="8" t="inlineStr">
+      <c r="O133" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13654,20 +13654,20 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L134" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M134" s="7" t="n">
+      <c r="M134" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -13675,7 +13675,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13751,20 +13751,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M135" s="7" t="n">
+      <c r="M135" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -13772,7 +13772,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13848,20 +13848,20 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M136" s="7" t="n">
+      <c r="M136" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -13869,7 +13869,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13953,12 +13953,12 @@
       <c r="K137" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="8" t="inlineStr">
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="7" t="n">
+      <c r="M137" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -13966,7 +13966,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O137" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14042,20 +14042,20 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="7" t="n">
+      <c r="M138" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14063,7 +14063,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="8" t="inlineStr">
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14139,20 +14139,20 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M139" s="7" t="n">
+      <c r="M139" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -14160,7 +14160,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14236,20 +14236,20 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M140" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -14257,7 +14257,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14333,20 +14333,20 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M141" s="7" t="n">
+      <c r="M141" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -14354,7 +14354,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14430,20 +14430,20 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M142" s="7" t="n">
+      <c r="M142" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -14451,7 +14451,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O142" s="8" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14527,20 +14527,20 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -14548,7 +14548,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -14624,20 +14624,20 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M144" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M144" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -14645,7 +14645,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O144" s="8" t="inlineStr">
+      <c r="O144" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14721,20 +14721,20 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M145" s="7" t="n">
+      <c r="M145" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -14742,7 +14742,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O145" s="8" t="inlineStr">
+      <c r="O145" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14818,20 +14818,20 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M146" s="7" t="n">
+      <c r="M146" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
@@ -14839,7 +14839,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O146" s="8" t="inlineStr">
+      <c r="O146" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14848,7 +14848,7 @@
         <v>3</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -14915,20 +14915,20 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M147" s="7" t="n">
+      <c r="M147" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -14936,7 +14936,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O147" s="8" t="inlineStr">
+      <c r="O147" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15012,20 +15012,20 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L148" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M148" s="7" t="n">
+      <c r="M148" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
@@ -15033,7 +15033,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O148" s="8" t="inlineStr">
+      <c r="O148" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15109,20 +15109,20 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M149" s="7" t="n">
+      <c r="M149" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -15130,7 +15130,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O149" s="8" t="inlineStr">
+      <c r="O149" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15154,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15206,20 +15206,20 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M150" s="7" t="n">
+      <c r="M150" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N150" s="4" t="inlineStr">
@@ -15227,7 +15227,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O150" s="8" t="inlineStr">
+      <c r="O150" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15303,20 +15303,20 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M151" s="7" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M151" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -15324,7 +15324,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O151" s="8" t="inlineStr">
+      <c r="O151" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15400,20 +15400,20 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M152" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -15421,7 +15421,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O152" s="8" t="inlineStr">
+      <c r="O152" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15497,20 +15497,20 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M153" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M153" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -15518,7 +15518,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O153" s="8" t="inlineStr">
+      <c r="O153" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15594,20 +15594,20 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L154" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M154" s="7" t="n">
+      <c r="M154" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -15615,7 +15615,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O154" s="8" t="inlineStr">
+      <c r="O154" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -15691,20 +15691,20 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M155" s="7" t="n">
+      <c r="M155" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -15712,7 +15712,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O155" s="8" t="inlineStr">
+      <c r="O155" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15788,20 +15788,20 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L156" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M156" s="7" t="n">
+      <c r="M156" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -15809,7 +15809,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O156" s="8" t="inlineStr">
+      <c r="O156" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15885,20 +15885,20 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M157" s="7" t="n">
+      <c r="M157" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -15906,7 +15906,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O157" s="8" t="inlineStr">
+      <c r="O157" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15982,20 +15982,20 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M158" s="7" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M158" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -16003,7 +16003,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O158" s="8" t="inlineStr">
+      <c r="O158" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16087,12 +16087,12 @@
       <c r="K159" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L159" s="8" t="inlineStr">
+      <c r="L159" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M159" s="7" t="n">
+      <c r="M159" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
@@ -16100,7 +16100,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O159" s="8" t="inlineStr">
+      <c r="O159" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16176,20 +16176,20 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M160" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M160" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -16197,7 +16197,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O160" s="8" t="inlineStr">
+      <c r="O160" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16206,13 +16206,13 @@
         <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -16221,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -16273,20 +16273,20 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M161" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L161" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M161" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -16294,7 +16294,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O161" s="8" t="inlineStr">
+      <c r="O161" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16370,20 +16370,20 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M162" s="7" t="n">
+      <c r="M162" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N162" s="4" t="inlineStr">
@@ -16391,7 +16391,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O162" s="8" t="inlineStr">
+      <c r="O162" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16467,20 +16467,20 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L163" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M163" s="7" t="n">
+      <c r="M163" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N163" s="4" t="inlineStr">
@@ -16488,7 +16488,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O163" s="8" t="inlineStr">
+      <c r="O163" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16564,20 +16564,20 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L164" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M164" s="7" t="n">
+      <c r="M164" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N164" s="4" t="inlineStr">
@@ -16585,7 +16585,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O164" s="8" t="inlineStr">
+      <c r="O164" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16661,20 +16661,20 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L165" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L165" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M165" s="7" t="n">
+      <c r="M165" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N165" s="4" t="inlineStr">
@@ -16682,7 +16682,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O165" s="8" t="inlineStr">
+      <c r="O165" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16706,7 +16706,7 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -16758,20 +16758,20 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L166" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M166" s="7" t="n">
+      <c r="M166" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -16779,7 +16779,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O166" s="8" t="inlineStr">
+      <c r="O166" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16803,7 +16803,7 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -16855,20 +16855,20 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M167" s="7" t="n">
+      <c r="M167" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
@@ -16876,7 +16876,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O167" s="8" t="inlineStr">
+      <c r="O167" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16952,20 +16952,20 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M168" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M168" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N168" s="4" t="inlineStr">
@@ -16973,7 +16973,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O168" s="8" t="inlineStr">
+      <c r="O168" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17049,20 +17049,20 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L169" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M169" s="7" t="n">
+      <c r="M169" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
@@ -17070,7 +17070,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O169" s="8" t="inlineStr">
+      <c r="O169" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17146,20 +17146,20 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M170" s="7" t="n">
+      <c r="M170" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N170" s="4" t="inlineStr">
@@ -17167,7 +17167,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O170" s="8" t="inlineStr">
+      <c r="O170" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17243,20 +17243,20 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M171" s="7" t="n">
+      <c r="M171" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
@@ -17264,7 +17264,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O171" s="8" t="inlineStr">
+      <c r="O171" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17340,20 +17340,20 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L172" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M172" s="7" t="n">
+      <c r="M172" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
@@ -17361,7 +17361,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O172" s="8" t="inlineStr">
+      <c r="O172" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17437,20 +17437,20 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M173" s="7" t="n">
+      <c r="M173" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
@@ -17458,7 +17458,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O173" s="8" t="inlineStr">
+      <c r="O173" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17485,7 +17485,7 @@
         <v>4</v>
       </c>
       <c r="W173" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X173" s="10" t="n">
         <v>6</v>
@@ -17534,20 +17534,20 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L174" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M174" s="7" t="n">
+      <c r="M174" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N174" s="4" t="inlineStr">
@@ -17555,7 +17555,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O174" s="8" t="inlineStr">
+      <c r="O174" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17631,20 +17631,20 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L175" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M175" s="7" t="n">
+      <c r="M175" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N175" s="4" t="inlineStr">
@@ -17652,7 +17652,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O175" s="8" t="inlineStr">
+      <c r="O175" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17736,12 +17736,12 @@
       <c r="K176" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L176" s="8" t="inlineStr">
+      <c r="L176" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M176" s="7" t="n">
+      <c r="M176" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N176" s="4" t="inlineStr">
@@ -17749,7 +17749,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O176" s="8" t="inlineStr">
+      <c r="O176" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,20 +17825,20 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M177" s="7" t="n">
+      <c r="M177" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N177" s="4" t="inlineStr">
@@ -17846,7 +17846,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O177" s="8" t="inlineStr">
+      <c r="O177" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17869,8 +17869,8 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>2</v>
+      <c r="V177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -17930,12 +17930,12 @@
       <c r="K178" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L178" s="8" t="inlineStr">
+      <c r="L178" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M178" s="7" t="n">
+      <c r="M178" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N178" s="4" t="inlineStr">
@@ -17943,7 +17943,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O178" s="8" t="inlineStr">
+      <c r="O178" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,20 +18019,20 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M179" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M179" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N179" s="4" t="inlineStr">
@@ -18040,7 +18040,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O179" s="8" t="inlineStr">
+      <c r="O179" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18063,8 +18063,8 @@
       <c r="U179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V179" s="9" t="n">
-        <v>3</v>
+      <c r="V179" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
@@ -18116,20 +18116,20 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M180" s="7" t="n">
+      <c r="M180" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N180" s="4" t="inlineStr">
@@ -18137,7 +18137,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O180" s="8" t="inlineStr">
+      <c r="O180" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18213,20 +18213,20 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M181" s="7" t="n">
+      <c r="M181" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -18234,7 +18234,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O181" s="8" t="inlineStr">
+      <c r="O181" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18310,20 +18310,20 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M182" s="7" t="n">
+      <c r="M182" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N182" s="4" t="inlineStr">
@@ -18331,7 +18331,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O182" s="8" t="inlineStr">
+      <c r="O182" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18407,20 +18407,20 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M183" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M183" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N183" s="4" t="inlineStr">
@@ -18428,7 +18428,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O183" s="8" t="inlineStr">
+      <c r="O183" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18504,20 +18504,20 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M184" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M184" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N184" s="4" t="inlineStr">
@@ -18525,7 +18525,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O184" s="8" t="inlineStr">
+      <c r="O184" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18549,7 +18549,7 @@
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
@@ -18601,20 +18601,20 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L185" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M185" s="7" t="n">
+      <c r="M185" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N185" s="4" t="inlineStr">
@@ -18622,7 +18622,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O185" s="8" t="inlineStr">
+      <c r="O185" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18698,20 +18698,20 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L186" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M186" s="7" t="n">
+      <c r="M186" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N186" s="4" t="inlineStr">
@@ -18719,7 +18719,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O186" s="8" t="inlineStr">
+      <c r="O186" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18781,7 +18781,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -18795,20 +18795,20 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M187" s="7" t="n">
+      <c r="M187" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N187" s="4" t="inlineStr">
@@ -18816,7 +18816,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O187" s="8" t="inlineStr">
+      <c r="O187" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18839,8 +18839,8 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="9" t="n">
-        <v>0</v>
+      <c r="V187" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
@@ -18892,20 +18892,20 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L188" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M188" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L188" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M188" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N188" s="4" t="inlineStr">
@@ -18913,7 +18913,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O188" s="8" t="inlineStr">
+      <c r="O188" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18989,20 +18989,20 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M189" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M189" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N189" s="4" t="inlineStr">
@@ -19010,7 +19010,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O189" s="8" t="inlineStr">
+      <c r="O189" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19086,20 +19086,20 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M190" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M190" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N190" s="4" t="inlineStr">
@@ -19107,7 +19107,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O190" s="8" t="inlineStr">
+      <c r="O190" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19131,7 +19131,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -19191,12 +19191,12 @@
       <c r="K191" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L191" s="8" t="inlineStr">
+      <c r="L191" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M191" s="7" t="n">
+      <c r="M191" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N191" s="4" t="inlineStr">
@@ -19204,7 +19204,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O191" s="8" t="inlineStr">
+      <c r="O191" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19228,7 +19228,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -19280,20 +19280,20 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M192" s="7" t="n">
+      <c r="M192" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N192" s="4" t="inlineStr">
@@ -19301,7 +19301,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O192" s="8" t="inlineStr">
+      <c r="O192" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19324,8 +19324,8 @@
       <c r="U192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V192" s="9" t="n">
-        <v>3</v>
+      <c r="V192" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
@@ -19377,20 +19377,20 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M193" s="7" t="n">
+      <c r="M193" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N193" s="4" t="inlineStr">
@@ -19398,7 +19398,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O193" s="8" t="inlineStr">
+      <c r="O193" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19474,20 +19474,20 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M194" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M194" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N194" s="4" t="inlineStr">
@@ -19495,7 +19495,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O194" s="8" t="inlineStr">
+      <c r="O194" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19571,20 +19571,20 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M195" s="7" t="n">
+      <c r="M195" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N195" s="4" t="inlineStr">
@@ -19592,7 +19592,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O195" s="8" t="inlineStr">
+      <c r="O195" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19668,20 +19668,20 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M196" s="7" t="n">
+      <c r="M196" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N196" s="4" t="inlineStr">
@@ -19689,7 +19689,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O196" s="8" t="inlineStr">
+      <c r="O196" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19765,20 +19765,20 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M197" s="7" t="n">
+      <c r="M197" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N197" s="4" t="inlineStr">
@@ -19786,7 +19786,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O197" s="8" t="inlineStr">
+      <c r="O197" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19810,7 +19810,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -19862,20 +19862,20 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L198" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M198" s="7" t="n">
+      <c r="M198" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N198" s="4" t="inlineStr">
@@ -19883,7 +19883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O198" s="8" t="inlineStr">
+      <c r="O198" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19907,7 +19907,7 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -19959,20 +19959,20 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L199" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M199" s="7" t="n">
+      <c r="M199" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N199" s="4" t="inlineStr">
@@ -19980,7 +19980,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O199" s="8" t="inlineStr">
+      <c r="O199" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -19997,14 +19997,14 @@
       <c r="S199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T199" s="9" t="n">
-        <v>0</v>
+      <c r="T199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U199" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V199" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W199" s="9" t="n">
         <v>0</v>
@@ -20056,20 +20056,20 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M200" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M200" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N200" s="4" t="inlineStr">
@@ -20077,7 +20077,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O200" s="8" t="inlineStr">
+      <c r="O200" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20153,20 +20153,20 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M201" s="7" t="n">
+      <c r="M201" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N201" s="4" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O201" s="8" t="inlineStr">
+      <c r="O201" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20250,20 +20250,20 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M202" s="7" t="n">
+      <c r="M202" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N202" s="4" t="inlineStr">
@@ -20271,7 +20271,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O202" s="8" t="inlineStr">
+      <c r="O202" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20347,20 +20347,20 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M203" s="7" t="n">
+      <c r="M203" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N203" s="4" t="inlineStr">
@@ -20368,7 +20368,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O203" s="8" t="inlineStr">
+      <c r="O203" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20444,20 +20444,20 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M204" s="7" t="n">
+      <c r="M204" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N204" s="4" t="inlineStr">
@@ -20465,7 +20465,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O204" s="8" t="inlineStr">
+      <c r="O204" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20541,20 +20541,20 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L205" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M205" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M205" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
@@ -20562,7 +20562,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O205" s="8" t="inlineStr">
+      <c r="O205" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20586,7 +20586,7 @@
         <v>1</v>
       </c>
       <c r="V205" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
@@ -20651,7 +20651,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M206" s="7" t="n">
+      <c r="M206" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
@@ -20659,7 +20659,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O206" s="8" t="inlineStr">
+      <c r="O206" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20683,7 +20683,7 @@
         <v>0</v>
       </c>
       <c r="V206" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W206" s="9" t="n">
         <v>0</v>
@@ -20735,20 +20735,20 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L207" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M207" s="7" t="n">
+      <c r="M207" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
@@ -20756,7 +20756,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O207" s="8" t="inlineStr">
+      <c r="O207" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20832,20 +20832,20 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L208" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M208" s="7" t="n">
+      <c r="M208" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N208" s="4" t="inlineStr">
@@ -20853,7 +20853,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O208" s="8" t="inlineStr">
+      <c r="O208" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -20929,20 +20929,20 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M209" s="7" t="n">
+      <c r="M209" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N209" s="4" t="inlineStr">
@@ -20950,7 +20950,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O209" s="8" t="inlineStr">
+      <c r="O209" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21026,20 +21026,20 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L210" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M210" s="7" t="n">
+      <c r="M210" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N210" s="4" t="inlineStr">
@@ -21047,7 +21047,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O210" s="8" t="inlineStr">
+      <c r="O210" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21071,7 +21071,7 @@
         <v>0</v>
       </c>
       <c r="V210" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W210" s="9" t="n">
         <v>0</v>
@@ -21123,20 +21123,20 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L211" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M211" s="7" t="n">
+      <c r="M211" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N211" s="4" t="inlineStr">
@@ -21144,7 +21144,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O211" s="8" t="inlineStr">
+      <c r="O211" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21220,20 +21220,20 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L212" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M212" s="7" t="n">
+      <c r="M212" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N212" s="4" t="inlineStr">
@@ -21241,7 +21241,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O212" s="8" t="inlineStr">
+      <c r="O212" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21317,20 +21317,20 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M213" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M213" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N213" s="4" t="inlineStr">
@@ -21338,7 +21338,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O213" s="8" t="inlineStr">
+      <c r="O213" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21414,20 +21414,20 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L214" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M214" s="7" t="n">
+      <c r="M214" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N214" s="4" t="inlineStr">
@@ -21435,7 +21435,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O214" s="8" t="inlineStr">
+      <c r="O214" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21511,20 +21511,20 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M215" s="7" t="n">
+      <c r="M215" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N215" s="4" t="inlineStr">
@@ -21532,7 +21532,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O215" s="8" t="inlineStr">
+      <c r="O215" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21608,20 +21608,20 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L216" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L216" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M216" s="7" t="n">
+      <c r="M216" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N216" s="4" t="inlineStr">
@@ -21629,7 +21629,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O216" s="8" t="inlineStr">
+      <c r="O216" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21705,20 +21705,20 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M217" s="7" t="n">
+      <c r="M217" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N217" s="4" t="inlineStr">
@@ -21726,7 +21726,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O217" s="8" t="inlineStr">
+      <c r="O217" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21802,20 +21802,20 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L218" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M218" s="7" t="n">
+      <c r="M218" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N218" s="4" t="inlineStr">
@@ -21823,7 +21823,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O218" s="8" t="inlineStr">
+      <c r="O218" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21899,20 +21899,20 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L219" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M219" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L219" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M219" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N219" s="4" t="inlineStr">
@@ -21920,7 +21920,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O219" s="8" t="inlineStr">
+      <c r="O219" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -21996,20 +21996,20 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L220" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L220" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M220" s="7" t="n">
+      <c r="M220" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N220" s="4" t="inlineStr">
@@ -22017,7 +22017,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O220" s="8" t="inlineStr">
+      <c r="O220" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22093,20 +22093,20 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K221" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L221" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M221" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L221" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M221" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N221" s="4" t="inlineStr">
@@ -22114,7 +22114,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O221" s="8" t="inlineStr">
+      <c r="O221" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22138,7 +22138,7 @@
         <v>0</v>
       </c>
       <c r="V221" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W221" s="9" t="n">
         <v>0</v>
@@ -22198,12 +22198,12 @@
       <c r="K222" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L222" s="8" t="inlineStr">
+      <c r="L222" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M222" s="7" t="n">
+      <c r="M222" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N222" s="4" t="inlineStr">
@@ -22211,7 +22211,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O222" s="8" t="inlineStr">
+      <c r="O222" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22235,7 +22235,7 @@
         <v>0</v>
       </c>
       <c r="V222" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W222" s="9" t="n">
         <v>0</v>
@@ -22295,12 +22295,12 @@
       <c r="K223" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L223" s="8" t="inlineStr">
+      <c r="L223" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M223" s="7" t="n">
+      <c r="M223" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N223" s="4" t="inlineStr">
@@ -22308,7 +22308,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O223" s="8" t="inlineStr">
+      <c r="O223" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22384,20 +22384,20 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L224" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L224" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M224" s="7" t="n">
+      <c r="M224" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N224" s="4" t="inlineStr">
@@ -22405,7 +22405,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O224" s="8" t="inlineStr">
+      <c r="O224" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22481,20 +22481,20 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L225" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M225" s="7" t="n">
+      <c r="M225" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N225" s="4" t="inlineStr">
@@ -22502,7 +22502,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O225" s="8" t="inlineStr">
+      <c r="O225" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22578,20 +22578,20 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L226" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M226" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L226" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M226" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N226" s="4" t="inlineStr">
@@ -22599,7 +22599,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O226" s="8" t="inlineStr">
+      <c r="O226" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22675,20 +22675,20 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L227" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L227" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M227" s="7" t="n">
+      <c r="M227" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N227" s="4" t="inlineStr">
@@ -22696,7 +22696,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O227" s="8" t="inlineStr">
+      <c r="O227" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22720,7 +22720,7 @@
         <v>0</v>
       </c>
       <c r="V227" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W227" s="9" t="n">
         <v>0</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F228" s="6" t="n">
         <v>10</v>
@@ -22772,20 +22772,20 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K228" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L228" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M228" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L228" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M228" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N228" s="4" t="inlineStr">
@@ -22793,7 +22793,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O228" s="8" t="inlineStr">
+      <c r="O228" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22810,8 +22810,8 @@
       <c r="S228" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T228" s="9" t="n">
-        <v>0</v>
+      <c r="T228" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U228" s="9" t="n">
         <v>0</v>
@@ -22869,20 +22869,20 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L229" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L229" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M229" s="7" t="n">
+      <c r="M229" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N229" s="4" t="inlineStr">
@@ -22890,7 +22890,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O229" s="8" t="inlineStr">
+      <c r="O229" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -22979,7 +22979,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M230" s="7" t="n">
+      <c r="M230" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N230" s="4" t="inlineStr">
@@ -22987,7 +22987,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O230" s="8" t="inlineStr">
+      <c r="O230" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -23132,7 +23132,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -23183,7 +23183,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -23297,7 +23297,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -23396,7 +23396,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -23429,7 +23429,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -23447,7 +23447,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -23462,7 +23462,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -23480,7 +23480,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23513,7 +23513,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -23528,7 +23528,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23594,7 +23594,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23627,7 +23627,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23645,7 +23645,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -23693,7 +23693,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -23711,7 +23711,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23726,7 +23726,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -23759,7 +23759,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -23777,7 +23777,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -23843,7 +23843,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -23858,7 +23858,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -23957,7 +23957,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -23975,7 +23975,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -24023,7 +24023,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24089,7 +24089,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -24221,7 +24221,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -24287,7 +24287,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -24338,7 +24338,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -24353,7 +24353,7 @@
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -24386,7 +24386,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -24404,7 +24404,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -24419,7 +24419,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -24437,7 +24437,7 @@
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -24452,7 +24452,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -24470,7 +24470,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -24485,7 +24485,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -24518,7 +24518,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -24584,7 +24584,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -24668,7 +24668,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -24683,7 +24683,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2149,8 +2149,8 @@
       <c r="S15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="9" t="n">
-        <v>0</v>
+      <c r="T15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3125,8 +3125,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>2</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>4</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4092,8 +4092,8 @@
       <c r="T35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
+      <c r="U35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V35" s="10" t="n">
         <v>4</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4483,8 +4483,8 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>3</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -6909,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="S67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -7199,8 +7199,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>2</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="10" t="n">
         <v>1</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>5</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17860,8 +17860,8 @@
       <c r="R177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S177" s="9" t="n">
-        <v>1</v>
+      <c r="S177" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T177" s="10" t="n">
         <v>1</v>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>5</v>
@@ -19571,13 +19571,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" s="9" t="n">
         <v>1</v>
@@ -19619,7 +19619,7 @@
         <v>4</v>
       </c>
       <c r="W195" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X195" s="10" t="n">
         <v>7</v>
@@ -20929,13 +20929,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
@@ -21705,13 +21705,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>0</v>
       </c>
       <c r="V217" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W217" s="9" t="n">
         <v>0</v>
@@ -21838,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="S218" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T218" s="9" t="n">
         <v>0</v>
@@ -22123,7 +22123,7 @@
         <v>1</v>
       </c>
       <c r="Q221" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R221" s="9" t="n">
         <v>0</v>
@@ -22772,17 +22772,17 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K228" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L228" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M228" s="8" t="n">
@@ -22817,7 +22817,7 @@
         <v>0</v>
       </c>
       <c r="V228" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W228" s="9" t="n">
         <v>0</v>
@@ -22869,13 +22869,13 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -23282,7 +23282,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -23315,13 +23315,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -23348,7 +23348,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23528,7 +23528,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -23546,7 +23546,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -24338,7 +24338,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -24683,7 +24683,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/220/inyear.xlsx
+++ b/docs/d/220/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -894,8 +894,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>3</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3322,8 +3322,8 @@
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>3</v>
+      <c r="W27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>4</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" s="10" t="n">
         <v>1</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -6999,14 +6999,14 @@
       <c r="S65" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
+      <c r="T65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J67" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>1</v>
@@ -7203,10 +7203,10 @@
         <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7837,10 +7837,10 @@
         <v>8</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8163,8 +8163,8 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9034,19 +9034,19 @@
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11717,10 +11717,10 @@
         <v>6</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140" s="10" t="n">
         <v>2</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>0</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -16220,8 +16220,8 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>3</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -18504,13 +18504,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         </is>
       </c>
       <c r="P185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q185" s="9" t="n">
         <v>0</v>
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19280,13 +19280,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>4</v>
       </c>
       <c r="W192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X192" s="10" t="n">
         <v>5</v>
@@ -20042,7 +20042,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -20085,8 +20085,8 @@
       <c r="P200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" s="9" t="n">
-        <v>1</v>
+      <c r="Q200" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R200" s="9" t="n">
         <v>0</v>
@@ -21109,7 +21109,7 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -21123,13 +21123,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
@@ -21161,8 +21161,8 @@
       <c r="S211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T211" s="9" t="n">
-        <v>0</v>
+      <c r="T211" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U211" s="9" t="n">
         <v>0</v>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         </is>
       </c>
       <c r="P228" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q228" s="9" t="n">
         <v>0</v>
@@ -23117,7 +23117,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -23282,7 +23282,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -23513,7 +23513,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -23612,7 +23612,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -23678,7 +23678,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -24206,7 +24206,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -24221,7 +24221,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -24470,7 +24470,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -24536,7 +24536,7 @@
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
